--- a/Templates/Template_SA-2_Catalogo_funzioni_di_sistema.xlsx
+++ b/Templates/Template_SA-2_Catalogo_funzioni_di_sistema.xlsx
@@ -578,8 +578,8 @@
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -613,7 +613,7 @@
     <row r="4" ht="39" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Come si compila. Un foglio per dominio. Nome con verbo e oggetto, senza sigle di modo, livello o paragrafo (D5). La disponibilità per modo si prende dalle righe 4.5.2-R01–R77. Una funzione nuova va proposta qui con la motivazione. In ATLAS è la scheda della funzione di sistema (SA-2); voci di bordo e ADR sono calcolate.</t>
+          <t>Come si compila. Un foglio per dominio. Nome con verbo e oggetto, senza sigle di modo, livello o paragrafo (D5). Le righe 4.5.2 sono quelle della tabella 4.5.2-R01–R77. Una funzione nuova va proposta qui con la motivazione. In ATLAS è la scheda della funzione di sistema (SA-2); voci di bordo e ADR sono calcolate.</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
+          <t>Requisiti derivati (SA-4)</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
           <t>Righe 4.5.2</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>Disponibilità nei modi (X / O)</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
+          <t>3.14.4.2-D1</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
           <t>4.5.2-R49</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>FS: X, SR: O</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
